--- a/TomaInventarioWEB/Plantillas/Plantilla_Reportes.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Reportes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Carlos Figueroa\Proyectos 2024\Toma Inventarios\Fuente\TomaInventario\TomaInventarioWEB_Sergio\TomaInventarioWEB\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046B1897-823A-4CB4-B7BF-F32D34DBF94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14778A0-0DDC-41DD-AD5B-1BD43E61E727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +82,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -92,13 +99,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,51 +155,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -210,60 +234,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1362074</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>857249</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>51027</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F202111-24C4-51DD-3C54-456642B0AF22}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect t="18070" b="17748"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13554074" y="95250"/>
-          <a:ext cx="2543175" cy="908277"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,144 +536,173 @@
   <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="22.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="9" width="22.85546875" style="6"/>
-    <col min="10" max="10" width="22.85546875" style="20"/>
-    <col min="11" max="11" width="22.85546875" style="14"/>
+    <col min="3" max="3" width="22.85546875" style="18"/>
+    <col min="4" max="10" width="22.85546875" style="19"/>
+    <col min="11" max="11" width="22.85546875" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="17"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="16"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="17"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="17"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="16"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="17"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="16"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="17"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="16"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="17"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="11"/>
-    </row>
-    <row r="8" spans="1:16" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="D8" s="8" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C8" s="17"/>
+      <c r="D8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="12"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="21"/>
     </row>
     <row r="9" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="11"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J10" s="18"/>
-      <c r="K10" s="11"/>
-    </row>
-    <row r="11" spans="1:16" s="10" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="13"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -713,6 +712,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>